--- a/tame_output/ON/bt/strategyON_20231218.xlsx
+++ b/tame_output/ON/bt/strategyON_20231218.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-99.0%</t>
+          <t>-98.9%</t>
         </is>
       </c>
     </row>
@@ -43261,16 +43261,16 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.4345780730065218</v>
+        <v>0.4350796250600922</v>
       </c>
       <c r="E1815" t="n">
-        <v>3.283151150421007</v>
+        <v>3.283351771242435</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.709382953608165</v>
+        <v>1.709376034355729</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.135306117697046</v>
+        <v>4.135301966145584</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231218.xlsx
+++ b/tame_output/ON/bt/strategyON_20231218.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-98.9%</t>
+          <t>-98.8%</t>
         </is>
       </c>
     </row>
@@ -43261,16 +43261,16 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.4350796250600922</v>
+        <v>0.4359407897923235</v>
       </c>
       <c r="E1815" t="n">
-        <v>3.283351771242435</v>
+        <v>3.283696237135328</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.709376034355729</v>
+        <v>1.709212455783763</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.135301966145584</v>
+        <v>4.135203819002404</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231218.xlsx
+++ b/tame_output/ON/bt/strategyON_20231218.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>483.6%</t>
+          <t>481.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-98.8%</t>
+          <t>-106.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-37.7%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>111.9%</t>
+          <t>112.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -43261,16 +43261,16 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.4359407897923235</v>
+        <v>0.3635903552494775</v>
       </c>
       <c r="E1815" t="n">
-        <v>3.283696237135328</v>
+        <v>3.254756063318189</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.709212455783763</v>
+        <v>1.715160640818068</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.135203819002404</v>
+        <v>4.138772730022988</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231218.xlsx
+++ b/tame_output/ON/bt/strategyON_20231218.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.8%</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>481.9%</t>
+          <t>480.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-162.5%</t>
+          <t>-162.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-106.1%</t>
+          <t>-106.7%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.9%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.1%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
     </row>
@@ -42272,10 +42272,10 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-2.972914543191393</v>
+        <v>-3.059142012195853</v>
       </c>
       <c r="E1772" t="n">
-        <v>1.867181815622271</v>
+        <v>1.832690828020487</v>
       </c>
       <c r="F1772" t="n">
         <v>0.3425749827949994</v>
@@ -42295,10 +42295,10 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-2.989922788594002</v>
+        <v>-3.076150257598462</v>
       </c>
       <c r="E1773" t="n">
-        <v>1.861456090098959</v>
+        <v>1.826965102497175</v>
       </c>
       <c r="F1773" t="n">
         <v>0.3455741178079732</v>
@@ -42318,10 +42318,10 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-2.970963066142648</v>
+        <v>-3.057190535147108</v>
       </c>
       <c r="E1774" t="n">
-        <v>1.869789841250774</v>
+        <v>1.835298853648989</v>
       </c>
       <c r="F1774" t="n">
         <v>0.3455741178079732</v>
@@ -42341,10 +42341,10 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-2.969728341539839</v>
+        <v>-3.055955810544299</v>
       </c>
       <c r="E1775" t="n">
-        <v>1.868519328555478</v>
+        <v>1.834028340953694</v>
       </c>
       <c r="F1775" t="n">
         <v>0.3455741178079732</v>
@@ -42364,10 +42364,10 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-2.979762605363488</v>
+        <v>-3.065990074367948</v>
       </c>
       <c r="E1776" t="n">
-        <v>1.86807323286288</v>
+        <v>1.833582245261096</v>
       </c>
       <c r="F1776" t="n">
         <v>0.3455741178079732</v>
@@ -42387,10 +42387,10 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-2.984801603661355</v>
+        <v>-3.071029072665815</v>
       </c>
       <c r="E1777" t="n">
-        <v>1.890039595433342</v>
+        <v>1.855548607831558</v>
       </c>
       <c r="F1777" t="n">
         <v>0.3405351195101065</v>
@@ -42410,10 +42410,10 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-2.974981885500804</v>
+        <v>-3.061209354505264</v>
       </c>
       <c r="E1778" t="n">
-        <v>1.891436194184792</v>
+        <v>1.856945206583008</v>
       </c>
       <c r="F1778" t="n">
         <v>0.3469650597267939</v>
@@ -42433,10 +42433,10 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-2.97318025866185</v>
+        <v>-3.05940772766631</v>
       </c>
       <c r="E1779" t="n">
-        <v>1.877405406924</v>
+        <v>1.842914419322216</v>
       </c>
       <c r="F1779" t="n">
         <v>0.3469650597267939</v>
@@ -42456,10 +42456,10 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-2.972191576917682</v>
+        <v>-3.058419045922142</v>
       </c>
       <c r="E1780" t="n">
-        <v>1.875914635937339</v>
+        <v>1.841423648335555</v>
       </c>
       <c r="F1780" t="n">
         <v>0.3469650597267939</v>
@@ -42479,10 +42479,10 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-2.964195222396143</v>
+        <v>-3.050422691400604</v>
       </c>
       <c r="E1781" t="n">
-        <v>1.881086804201795</v>
+        <v>1.84659581660001</v>
       </c>
       <c r="F1781" t="n">
         <v>0.3549614142483324</v>
@@ -42502,10 +42502,10 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-2.959211471724235</v>
+        <v>-3.045438940728695</v>
       </c>
       <c r="E1782" t="n">
-        <v>1.89491888506147</v>
+        <v>1.860427897459686</v>
       </c>
       <c r="F1782" t="n">
         <v>0.3599451649202411</v>
@@ -42525,10 +42525,10 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-2.952825332774679</v>
+        <v>-3.039052801779139</v>
       </c>
       <c r="E1783" t="n">
-        <v>1.904201543653081</v>
+        <v>1.869710556051297</v>
       </c>
       <c r="F1783" t="n">
         <v>0.3599451649202411</v>
@@ -42548,10 +42548,10 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-2.964630683093312</v>
+        <v>-3.050858152097772</v>
       </c>
       <c r="E1784" t="n">
-        <v>1.903495492285171</v>
+        <v>1.869004504683387</v>
       </c>
       <c r="F1784" t="n">
         <v>0.3481398146016085</v>
@@ -42571,10 +42571,10 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-2.955898872314646</v>
+        <v>-3.042126341319106</v>
       </c>
       <c r="E1785" t="n">
-        <v>1.912935674206526</v>
+        <v>1.878444686604742</v>
       </c>
       <c r="F1785" t="n">
         <v>0.3568716253802748</v>
@@ -42594,10 +42594,10 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-2.949561985670194</v>
+        <v>-3.035789454674654</v>
       </c>
       <c r="E1786" t="n">
-        <v>1.910781247812293</v>
+        <v>1.876290260210508</v>
       </c>
       <c r="F1786" t="n">
         <v>0.3568716253802748</v>
@@ -42617,10 +42617,10 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-2.947027537942825</v>
+        <v>-3.033255006947285</v>
       </c>
       <c r="E1787" t="n">
-        <v>1.921757684705434</v>
+        <v>1.88726669710365</v>
       </c>
       <c r="F1787" t="n">
         <v>0.3568716253802748</v>
@@ -42640,10 +42640,10 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-2.94710343692343</v>
+        <v>-3.03333090592789</v>
       </c>
       <c r="E1788" t="n">
-        <v>1.914142005306102</v>
+        <v>1.879651017704318</v>
       </c>
       <c r="F1788" t="n">
         <v>0.3576348860696016</v>
@@ -42663,10 +42663,10 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-2.957605626482776</v>
+        <v>-3.043833095487237</v>
       </c>
       <c r="E1789" t="n">
-        <v>1.887705705272736</v>
+        <v>1.853214717670952</v>
       </c>
       <c r="F1789" t="n">
         <v>0.347132696510255</v>
@@ -42686,10 +42686,10 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-2.959438889161893</v>
+        <v>-3.045666358166353</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.887673240047212</v>
+        <v>1.853182252445427</v>
       </c>
       <c r="F1790" t="n">
         <v>0.347132696510255</v>
@@ -42709,10 +42709,10 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-2.964448004223477</v>
+        <v>-3.050675473227937</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.886186673851437</v>
+        <v>1.851695686249653</v>
       </c>
       <c r="F1791" t="n">
         <v>0.3461381189517203</v>
@@ -42732,10 +42732,10 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-2.968153560860291</v>
+        <v>-3.054381029864751</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.883932176437077</v>
+        <v>1.849441188835293</v>
       </c>
       <c r="F1792" t="n">
         <v>0.3442684436940854</v>
@@ -42755,10 +42755,10 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-2.966921235502926</v>
+        <v>-3.053148704507386</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.884844958642342</v>
+        <v>1.850353971040558</v>
       </c>
       <c r="F1793" t="n">
         <v>0.3448988200661229</v>
@@ -42778,10 +42778,10 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-2.956593238487073</v>
+        <v>-3.042820707491534</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.893106065612897</v>
+        <v>1.858615078011113</v>
       </c>
       <c r="F1794" t="n">
         <v>0.3552268170819751</v>
@@ -42801,10 +42801,10 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-2.956476903339518</v>
+        <v>-3.042704372343978</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.899673259873755</v>
+        <v>1.865182272271971</v>
       </c>
       <c r="F1795" t="n">
         <v>0.3553431522295308</v>
@@ -42824,10 +42824,10 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-2.958322312916385</v>
+        <v>-3.044549781920845</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.895909066488397</v>
+        <v>1.861418078886613</v>
       </c>
       <c r="F1796" t="n">
         <v>0.3553431522295308</v>
@@ -42847,10 +42847,10 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-2.956823880391286</v>
+        <v>-3.043051349395746</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.89644672735957</v>
+        <v>1.861955739757786</v>
       </c>
       <c r="F1797" t="n">
         <v>0.3568415847546297</v>
@@ -42870,10 +42870,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-2.96488813258402</v>
+        <v>-3.05111560158848</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.894499004425788</v>
+        <v>1.860008016824004</v>
       </c>
       <c r="F1798" t="n">
         <v>0.3487773325618959</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-2.966218100045232</v>
+        <v>-3.052445569049692</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.893967017441303</v>
+        <v>1.859476029839519</v>
       </c>
       <c r="F1799" t="n">
         <v>0.3487773325618959</v>
@@ -42916,10 +42916,10 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-2.738353417311721</v>
+        <v>-2.824580886316181</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.98732936364187</v>
+        <v>1.952838376040086</v>
       </c>
       <c r="F1800" t="n">
         <v>0.3487773325618959</v>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-2.490251853444504</v>
+        <v>-2.576479322448964</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.094104585533849</v>
+        <v>2.059613597932065</v>
       </c>
       <c r="F1801" t="n">
         <v>0.3487773325618959</v>
@@ -42962,10 +42962,10 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-2.193413454051174</v>
+        <v>-2.279640923055634</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.214262956264638</v>
+        <v>2.179771968662854</v>
       </c>
       <c r="F1802" t="n">
         <v>0.4636318210430236</v>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-1.889773897225738</v>
+        <v>-1.976001366230198</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.337395853460499</v>
+        <v>2.302904865858715</v>
       </c>
       <c r="F1803" t="n">
         <v>0.4636318210430236</v>
@@ -43008,10 +43008,10 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-1.600753290785029</v>
+        <v>-1.686980759789489</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.44894351748624</v>
+        <v>2.414452529884456</v>
       </c>
       <c r="F1804" t="n">
         <v>0.4636318210430236</v>
@@ -43031,10 +43031,10 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-1.316033363521132</v>
+        <v>-1.402260832525592</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.568051627735817</v>
+        <v>2.533560640134033</v>
       </c>
       <c r="F1805" t="n">
         <v>0.7483517483069207</v>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-1.032271694029592</v>
+        <v>-1.118499163034052</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.68686845870624</v>
+        <v>2.652377471104456</v>
       </c>
       <c r="F1806" t="n">
         <v>0.7483517483069207</v>
@@ -43077,10 +43077,10 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-0.7706232996369509</v>
+        <v>-0.8568507686414111</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.784770403909929</v>
+        <v>2.750279416308146</v>
       </c>
       <c r="F1807" t="n">
         <v>1.010000142699561</v>
@@ -43100,10 +43100,10 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-0.4564568614976184</v>
+        <v>-0.5426843305020786</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.907900654181775</v>
+        <v>2.873409666579991</v>
       </c>
       <c r="F1808" t="n">
         <v>1.324166580838894</v>
@@ -43123,10 +43123,10 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-0.333945157391846</v>
+        <v>-0.4201726263963063</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.975319719450823</v>
+        <v>2.940828731849039</v>
       </c>
       <c r="F1809" t="n">
         <v>1.446678284944666</v>
@@ -43146,10 +43146,10 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-0.1725566234651177</v>
+        <v>-0.2587840924695779</v>
       </c>
       <c r="E1810" t="n">
-        <v>3.049691257076993</v>
+        <v>3.015200269475209</v>
       </c>
       <c r="F1810" t="n">
         <v>1.608066818871395</v>
@@ -43169,10 +43169,10 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>0.00718956768338852</v>
+        <v>-0.07903790132107169</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.135117345588327</v>
+        <v>3.100626357986543</v>
       </c>
       <c r="F1811" t="n">
         <v>1.608066818871395</v>
@@ -43192,10 +43192,10 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>0.1659904941546114</v>
+        <v>0.07976302515015121</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.205225096428082</v>
+        <v>3.170734108826298</v>
       </c>
       <c r="F1812" t="n">
         <v>1.608066818871395</v>
@@ -43215,10 +43215,10 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>0.2587789524599883</v>
+        <v>0.1725514834555281</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.231251228184939</v>
+        <v>3.196760240583155</v>
       </c>
       <c r="F1813" t="n">
         <v>1.700855277176772</v>
@@ -43238,10 +43238,10 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>0.3527994478308302</v>
+        <v>0.26657197882637</v>
       </c>
       <c r="E1814" t="n">
-        <v>3.264459923844</v>
+        <v>3.229968936242216</v>
       </c>
       <c r="F1814" t="n">
         <v>1.710697717669755</v>
@@ -43255,22 +43255,22 @@
         <v>45277</v>
       </c>
       <c r="B1815" t="n">
-        <v>3.095412751484652</v>
+        <v>3.103633701908235</v>
       </c>
       <c r="C1815" t="n">
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.3635903552494775</v>
+        <v>0.356674946732893</v>
       </c>
       <c r="E1815" t="n">
-        <v>3.254756063318189</v>
+        <v>3.251989899911556</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.715160640818068</v>
+        <v>1.713755911957541</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.138772730022988</v>
+        <v>4.137929892706671</v>
       </c>
     </row>
   </sheetData>
